--- a/docs/downloads/04/tbl_other_act_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_ambatoharanana.xlsx
@@ -405,12 +405,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Éleveur</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -459,12 +447,6 @@
           <t>Étudiant</t>
         </is>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -566,12 +548,6 @@
         <is>
           <t>Pêcheur exploitant</t>
         </is>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
       </c>
     </row>
     <row r="13">

--- a/docs/downloads/04/tbl_other_act_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/04/tbl_other_act_alaotra_ambatoharanana.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,14 +384,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>52</v>
-      </c>
-      <c r="D2">
-        <v>55.3</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -402,7 +396,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -414,14 +408,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C4">
         <v>37</v>
       </c>
       <c r="D4">
-        <v>39.4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -432,7 +426,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -444,7 +438,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
     </row>
@@ -456,14 +450,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C7">
-        <v>827</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>56.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
@@ -474,14 +468,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C8">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D8">
-        <v>3.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="9">
@@ -492,14 +486,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C9">
-        <v>64</v>
+        <v>391</v>
       </c>
       <c r="D9">
-        <v>4.4</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="10">
@@ -510,14 +504,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C10">
-        <v>391</v>
+        <v>35</v>
       </c>
       <c r="D10">
-        <v>26.7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="11">
@@ -528,14 +522,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="C11">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="12">
@@ -546,8 +540,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>76</v>
+      </c>
+      <c r="D12">
+        <v>10.3</v>
       </c>
     </row>
     <row r="13">
@@ -558,32 +558,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D13">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>51</v>
-      </c>
-      <c r="D14">
-        <v>3.5</v>
+        <v>11.4</v>
       </c>
     </row>
   </sheetData>
